--- a/artfynd/A 49269-2024 artfynd.xlsx
+++ b/artfynd/A 49269-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1371,6 +1371,126 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>121569491</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57371</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Granskogen v åhagen, Eret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>570659</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6693918</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-12-12</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-12-12</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Elisabeth Norman</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Elisabeth Norman</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49269-2024 artfynd.xlsx
+++ b/artfynd/A 49269-2024 artfynd.xlsx
@@ -1376,7 +1376,7 @@
         <v>121569491</v>
       </c>
       <c r="B8" t="n">
-        <v>57371</v>
+        <v>57372</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 49269-2024 artfynd.xlsx
+++ b/artfynd/A 49269-2024 artfynd.xlsx
@@ -1376,7 +1376,7 @@
         <v>121569491</v>
       </c>
       <c r="B8" t="n">
-        <v>57372</v>
+        <v>57373</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 49269-2024 artfynd.xlsx
+++ b/artfynd/A 49269-2024 artfynd.xlsx
@@ -1376,7 +1376,7 @@
         <v>121569491</v>
       </c>
       <c r="B8" t="n">
-        <v>57373</v>
+        <v>57381</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 49269-2024 artfynd.xlsx
+++ b/artfynd/A 49269-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1611,6 +1611,130 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>125952802</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57648</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Granskog, vägen, Eret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>570742</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6693877</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Flög upp från marken i planterade granskogen</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Elisabeth Norman</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Elisabeth Norman</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49269-2024 artfynd.xlsx
+++ b/artfynd/A 49269-2024 artfynd.xlsx
@@ -1616,7 +1616,7 @@
         <v>125952802</v>
       </c>
       <c r="B10" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 49269-2024 artfynd.xlsx
+++ b/artfynd/A 49269-2024 artfynd.xlsx
@@ -1616,7 +1616,7 @@
         <v>125952802</v>
       </c>
       <c r="B10" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 49269-2024 artfynd.xlsx
+++ b/artfynd/A 49269-2024 artfynd.xlsx
@@ -1616,7 +1616,7 @@
         <v>125952802</v>
       </c>
       <c r="B10" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 49269-2024 artfynd.xlsx
+++ b/artfynd/A 49269-2024 artfynd.xlsx
@@ -1740,7 +1740,7 @@
         <v>126876859</v>
       </c>
       <c r="B11" t="n">
-        <v>57651</v>
+        <v>57655</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 49269-2024 artfynd.xlsx
+++ b/artfynd/A 49269-2024 artfynd.xlsx
@@ -1740,7 +1740,7 @@
         <v>126876859</v>
       </c>
       <c r="B11" t="n">
-        <v>57655</v>
+        <v>57657</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 49269-2024 artfynd.xlsx
+++ b/artfynd/A 49269-2024 artfynd.xlsx
@@ -1740,7 +1740,7 @@
         <v>126876859</v>
       </c>
       <c r="B11" t="n">
-        <v>57657</v>
+        <v>57651</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
